--- a/Assets/equip_data.xlsx
+++ b/Assets/equip_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UNITY\gompang-survivor\Assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16E7AC0D-32C7-4F68-9B2F-D419BEF4F7B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD418403-1D82-4482-ABAF-BA38A7C10226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6609E6BD-B421-4305-A941-8033F08D5DC9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="89">
   <si>
     <t>Common</t>
   </si>
@@ -586,6 +586,196 @@
       <t>증가</t>
     </r>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BodyArmor</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BodyArmor1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>BodyArmor2</t>
+  </si>
+  <si>
+    <t>BodyArmor3</t>
+  </si>
+  <si>
+    <t>BodyArmor4</t>
+  </si>
+  <si>
+    <t>BodyArmor5</t>
+  </si>
+  <si>
+    <t>BodyArmor6</t>
+  </si>
+  <si>
+    <t>BodyArmor7</t>
+  </si>
+  <si>
+    <t>BodyArmor8</t>
+  </si>
+  <si>
+    <t>BodyArmor9</t>
+  </si>
+  <si>
+    <t>BodyArmor10</t>
+  </si>
+  <si>
+    <t>FlyDron1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FlyDron2</t>
+  </si>
+  <si>
+    <t>FlyDron3</t>
+  </si>
+  <si>
+    <t>FlyDron4</t>
+  </si>
+  <si>
+    <t>FlyDron5</t>
+  </si>
+  <si>
+    <t>FlyDron6</t>
+  </si>
+  <si>
+    <t>FlyDron7</t>
+  </si>
+  <si>
+    <t>FlyDron8</t>
+  </si>
+  <si>
+    <t>FlyDron9</t>
+  </si>
+  <si>
+    <t>FlyDron10</t>
+  </si>
+  <si>
+    <t>Gloves1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gloves2</t>
+  </si>
+  <si>
+    <t>Gloves3</t>
+  </si>
+  <si>
+    <t>Gloves4</t>
+  </si>
+  <si>
+    <t>Gloves5</t>
+  </si>
+  <si>
+    <t>Gloves6</t>
+  </si>
+  <si>
+    <t>Gloves7</t>
+  </si>
+  <si>
+    <t>Gloves8</t>
+  </si>
+  <si>
+    <t>Gloves9</t>
+  </si>
+  <si>
+    <t>Gloves10</t>
+  </si>
+  <si>
+    <t>Necklaces1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Necklaces2</t>
+  </si>
+  <si>
+    <t>Necklaces3</t>
+  </si>
+  <si>
+    <t>Necklaces4</t>
+  </si>
+  <si>
+    <t>Necklaces5</t>
+  </si>
+  <si>
+    <t>Necklaces6</t>
+  </si>
+  <si>
+    <t>Necklaces7</t>
+  </si>
+  <si>
+    <t>Necklaces8</t>
+  </si>
+  <si>
+    <t>Necklaces9</t>
+  </si>
+  <si>
+    <t>Necklaces10</t>
+  </si>
+  <si>
+    <t>Pants1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Pants2</t>
+  </si>
+  <si>
+    <t>Pants3</t>
+  </si>
+  <si>
+    <t>Pants4</t>
+  </si>
+  <si>
+    <t>Pants5</t>
+  </si>
+  <si>
+    <t>Pants6</t>
+  </si>
+  <si>
+    <t>Pants7</t>
+  </si>
+  <si>
+    <t>Pants8</t>
+  </si>
+  <si>
+    <t>Pants9</t>
+  </si>
+  <si>
+    <t>Pants10</t>
+  </si>
+  <si>
+    <t>Ring1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Ring2</t>
+  </si>
+  <si>
+    <t>Ring3</t>
+  </si>
+  <si>
+    <t>Ring4</t>
+  </si>
+  <si>
+    <t>Ring5</t>
+  </si>
+  <si>
+    <t>Ring6</t>
+  </si>
+  <si>
+    <t>Ring7</t>
+  </si>
+  <si>
+    <t>Ring8</t>
+  </si>
+  <si>
+    <t>Ring9</t>
+  </si>
+  <si>
+    <t>Ring10</t>
   </si>
 </sst>
 </file>
@@ -736,7 +926,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -787,6 +977,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1126,7 +1319,7 @@
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="14.69921875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.3984375" customWidth="1"/>
     <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.5" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="14" customWidth="1"/>
@@ -1168,10 +1361,10 @@
     </row>
     <row r="2" spans="1:16" ht="19.2" x14ac:dyDescent="0.4">
       <c r="A2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10">
-        <v>1</v>
+        <v>28</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>29</v>
       </c>
       <c r="C2" s="14">
         <v>0</v>
@@ -1195,7 +1388,7 @@
         <v>19</v>
       </c>
       <c r="J2" s="6">
-        <f>H2 / SUM($H$2:$H$7)*100</f>
+        <f t="shared" ref="J2:J7" si="0">H2 / SUM($H$2:$H$7)*100</f>
         <v>31.746031746031743</v>
       </c>
       <c r="K2" s="1"/>
@@ -1209,8 +1402,8 @@
       <c r="A3" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="10">
-        <v>2</v>
+      <c r="B3" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="C3" s="14">
         <v>0</v>
@@ -1234,7 +1427,7 @@
         <v>19</v>
       </c>
       <c r="J3" s="6">
-        <f>H3 / SUM($H$2:$H$7)*100</f>
+        <f t="shared" si="0"/>
         <v>28.571428571428569</v>
       </c>
       <c r="K3" s="1"/>
@@ -1248,8 +1441,8 @@
       <c r="A4" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="10">
-        <v>3</v>
+      <c r="B4" s="17" t="s">
+        <v>31</v>
       </c>
       <c r="C4" s="14">
         <v>0</v>
@@ -1273,7 +1466,7 @@
         <v>19</v>
       </c>
       <c r="J4" s="6">
-        <f>H4 / SUM($H$2:$H$7)*100</f>
+        <f t="shared" si="0"/>
         <v>25.396825396825395</v>
       </c>
       <c r="K4" s="1"/>
@@ -1287,8 +1480,8 @@
       <c r="A5" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B5" s="10">
-        <v>4</v>
+      <c r="B5" s="17" t="s">
+        <v>32</v>
       </c>
       <c r="C5" s="14">
         <v>0</v>
@@ -1312,7 +1505,7 @@
         <v>19</v>
       </c>
       <c r="J5" s="6">
-        <f>H5 / SUM($H$2:$H$7)*100</f>
+        <f t="shared" si="0"/>
         <v>6.3492063492063489</v>
       </c>
       <c r="K5" s="2" t="s">
@@ -1333,8 +1526,8 @@
       <c r="A6" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="10">
-        <v>5</v>
+      <c r="B6" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="C6" s="14">
         <v>0</v>
@@ -1358,7 +1551,7 @@
         <v>19</v>
       </c>
       <c r="J6" s="6">
-        <f>H6 / SUM($H$2:$H$7)*100</f>
+        <f t="shared" si="0"/>
         <v>4.7619047619047619</v>
       </c>
       <c r="K6" s="2" t="s">
@@ -1368,7 +1561,7 @@
         <v>150</v>
       </c>
       <c r="M6" s="1">
-        <f t="shared" ref="M6:M10" si="0">L6/SUM($L$5:$L$10)*100</f>
+        <f t="shared" ref="M6:M10" si="1">L6/SUM($L$5:$L$10)*100</f>
         <v>29.411764705882355</v>
       </c>
       <c r="N6" s="1"/>
@@ -1379,8 +1572,8 @@
       <c r="A7" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="10">
-        <v>6</v>
+      <c r="B7" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="C7" s="14">
         <v>0</v>
@@ -1404,7 +1597,7 @@
         <v>19</v>
       </c>
       <c r="J7" s="6">
-        <f>H7 / SUM($H$2:$H$7)*100</f>
+        <f t="shared" si="0"/>
         <v>3.1746031746031744</v>
       </c>
       <c r="K7" s="2" t="s">
@@ -1414,7 +1607,7 @@
         <v>100</v>
       </c>
       <c r="M7" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>19.607843137254903</v>
       </c>
       <c r="N7" s="1"/>
@@ -1425,8 +1618,8 @@
       <c r="A8" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="10">
-        <v>7</v>
+      <c r="B8" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="C8" s="14">
         <v>0</v>
@@ -1457,7 +1650,7 @@
         <v>30</v>
       </c>
       <c r="M8" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>5.8823529411764701</v>
       </c>
       <c r="N8" s="4" t="s">
@@ -1475,8 +1668,8 @@
       <c r="A9" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B9" s="10">
-        <v>8</v>
+      <c r="B9" s="17" t="s">
+        <v>36</v>
       </c>
       <c r="C9" s="14">
         <v>0</v>
@@ -1507,7 +1700,7 @@
         <v>20</v>
       </c>
       <c r="M9" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>3.9215686274509802</v>
       </c>
       <c r="N9" s="4" t="s">
@@ -1517,7 +1710,7 @@
         <v>20</v>
       </c>
       <c r="P9" s="1">
-        <f t="shared" ref="P9:P11" si="1">O9/SUM($O$8:$O$11)*100</f>
+        <f t="shared" ref="P9:P11" si="2">O9/SUM($O$8:$O$11)*100</f>
         <v>32.258064516129032</v>
       </c>
     </row>
@@ -1525,8 +1718,8 @@
       <c r="A10" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="10">
-        <v>9</v>
+      <c r="B10" s="17" t="s">
+        <v>37</v>
       </c>
       <c r="C10" s="14">
         <v>0</v>
@@ -1557,7 +1750,7 @@
         <v>10</v>
       </c>
       <c r="M10" s="1">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>1.9607843137254901</v>
       </c>
       <c r="N10" s="4" t="s">
@@ -1567,7 +1760,7 @@
         <v>10</v>
       </c>
       <c r="P10" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>16.129032258064516</v>
       </c>
     </row>
@@ -1575,8 +1768,8 @@
       <c r="A11" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="B11" s="10">
-        <v>10</v>
+      <c r="B11" s="17" t="s">
+        <v>38</v>
       </c>
       <c r="C11" s="10">
         <v>0.1</v>
@@ -1610,7 +1803,7 @@
         <v>2</v>
       </c>
       <c r="P11" s="1">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>3.225806451612903</v>
       </c>
     </row>
@@ -1618,8 +1811,8 @@
       <c r="A12" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="10">
-        <v>1</v>
+      <c r="B12" s="13" t="s">
+        <v>39</v>
       </c>
       <c r="C12" s="10">
         <v>5.0000000000000001E-3</v>
@@ -1647,8 +1840,8 @@
       <c r="A13" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="10">
-        <v>2</v>
+      <c r="B13" s="13" t="s">
+        <v>40</v>
       </c>
       <c r="C13" s="10">
         <v>0.01</v>
@@ -1676,8 +1869,8 @@
       <c r="A14" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="10">
-        <v>3</v>
+      <c r="B14" s="13" t="s">
+        <v>41</v>
       </c>
       <c r="C14" s="10">
         <v>1.4999999999999999E-2</v>
@@ -1705,8 +1898,8 @@
       <c r="A15" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B15" s="10">
-        <v>4</v>
+      <c r="B15" s="13" t="s">
+        <v>42</v>
       </c>
       <c r="C15" s="10">
         <v>0.02</v>
@@ -1734,8 +1927,8 @@
       <c r="A16" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B16" s="10">
-        <v>5</v>
+      <c r="B16" s="13" t="s">
+        <v>43</v>
       </c>
       <c r="C16" s="10">
         <v>2.5000000000000001E-2</v>
@@ -1763,8 +1956,8 @@
       <c r="A17" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B17" s="10">
-        <v>6</v>
+      <c r="B17" s="13" t="s">
+        <v>44</v>
       </c>
       <c r="C17" s="10">
         <v>0.03</v>
@@ -1792,8 +1985,8 @@
       <c r="A18" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B18" s="10">
-        <v>7</v>
+      <c r="B18" s="13" t="s">
+        <v>45</v>
       </c>
       <c r="C18" s="10">
         <v>0.05</v>
@@ -1819,8 +2012,8 @@
       <c r="A19" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B19" s="10">
-        <v>8</v>
+      <c r="B19" s="13" t="s">
+        <v>46</v>
       </c>
       <c r="C19" s="10">
         <v>0.1</v>
@@ -1846,8 +2039,8 @@
       <c r="A20" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="10">
-        <v>9</v>
+      <c r="B20" s="13" t="s">
+        <v>47</v>
       </c>
       <c r="C20" s="10">
         <v>0.125</v>
@@ -1873,8 +2066,8 @@
       <c r="A21" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="B21" s="10">
-        <v>10</v>
+      <c r="B21" s="13" t="s">
+        <v>48</v>
       </c>
       <c r="C21" s="10">
         <v>0.25</v>
@@ -1898,8 +2091,8 @@
       <c r="A22" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B22" s="10">
-        <v>1</v>
+      <c r="B22" s="13" t="s">
+        <v>49</v>
       </c>
       <c r="C22" s="14">
         <v>0</v>
@@ -1927,8 +2120,8 @@
       <c r="A23" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B23" s="10">
-        <v>2</v>
+      <c r="B23" s="13" t="s">
+        <v>50</v>
       </c>
       <c r="C23" s="14">
         <v>0</v>
@@ -1956,8 +2149,8 @@
       <c r="A24" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B24" s="10">
-        <v>3</v>
+      <c r="B24" s="13" t="s">
+        <v>51</v>
       </c>
       <c r="C24" s="14">
         <v>0</v>
@@ -1985,8 +2178,8 @@
       <c r="A25" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B25" s="10">
-        <v>4</v>
+      <c r="B25" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="C25" s="14">
         <v>0</v>
@@ -2014,8 +2207,8 @@
       <c r="A26" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B26" s="10">
-        <v>5</v>
+      <c r="B26" s="13" t="s">
+        <v>53</v>
       </c>
       <c r="C26" s="14">
         <v>0</v>
@@ -2043,8 +2236,8 @@
       <c r="A27" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B27" s="10">
-        <v>6</v>
+      <c r="B27" s="13" t="s">
+        <v>54</v>
       </c>
       <c r="C27" s="14">
         <v>0</v>
@@ -2072,8 +2265,8 @@
       <c r="A28" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B28" s="10">
-        <v>7</v>
+      <c r="B28" s="13" t="s">
+        <v>55</v>
       </c>
       <c r="C28" s="14">
         <v>0</v>
@@ -2101,8 +2294,8 @@
       <c r="A29" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B29" s="10">
-        <v>8</v>
+      <c r="B29" s="13" t="s">
+        <v>56</v>
       </c>
       <c r="C29" s="14">
         <v>0</v>
@@ -2130,8 +2323,8 @@
       <c r="A30" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B30" s="10">
-        <v>9</v>
+      <c r="B30" s="13" t="s">
+        <v>57</v>
       </c>
       <c r="C30" s="14">
         <v>0</v>
@@ -2159,8 +2352,8 @@
       <c r="A31" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="B31" s="10">
-        <v>10</v>
+      <c r="B31" s="13" t="s">
+        <v>58</v>
       </c>
       <c r="C31" s="10">
         <v>0.1</v>
@@ -2188,8 +2381,8 @@
       <c r="A32" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B32" s="10">
-        <v>1</v>
+      <c r="B32" s="13" t="s">
+        <v>59</v>
       </c>
       <c r="C32" s="10">
         <v>5.0000000000000001E-3</v>
@@ -2217,8 +2410,8 @@
       <c r="A33" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B33" s="10">
-        <v>2</v>
+      <c r="B33" s="13" t="s">
+        <v>60</v>
       </c>
       <c r="C33" s="10">
         <v>0.01</v>
@@ -2246,8 +2439,8 @@
       <c r="A34" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B34" s="10">
-        <v>3</v>
+      <c r="B34" s="13" t="s">
+        <v>61</v>
       </c>
       <c r="C34" s="10">
         <v>1.4999999999999999E-2</v>
@@ -2275,8 +2468,8 @@
       <c r="A35" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B35" s="10">
-        <v>4</v>
+      <c r="B35" s="13" t="s">
+        <v>62</v>
       </c>
       <c r="C35" s="10">
         <v>0.02</v>
@@ -2304,8 +2497,8 @@
       <c r="A36" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B36" s="10">
-        <v>5</v>
+      <c r="B36" s="13" t="s">
+        <v>63</v>
       </c>
       <c r="C36" s="10">
         <v>2.5000000000000001E-2</v>
@@ -2333,8 +2526,8 @@
       <c r="A37" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B37" s="10">
-        <v>6</v>
+      <c r="B37" s="13" t="s">
+        <v>64</v>
       </c>
       <c r="C37" s="10">
         <v>0.03</v>
@@ -2362,8 +2555,8 @@
       <c r="A38" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B38" s="10">
-        <v>7</v>
+      <c r="B38" s="13" t="s">
+        <v>65</v>
       </c>
       <c r="C38" s="10">
         <v>0.05</v>
@@ -2391,8 +2584,8 @@
       <c r="A39" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B39" s="10">
-        <v>8</v>
+      <c r="B39" s="13" t="s">
+        <v>66</v>
       </c>
       <c r="C39" s="10">
         <v>0.1</v>
@@ -2420,8 +2613,8 @@
       <c r="A40" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B40" s="10">
-        <v>9</v>
+      <c r="B40" s="13" t="s">
+        <v>67</v>
       </c>
       <c r="C40" s="10">
         <v>0.125</v>
@@ -2449,8 +2642,8 @@
       <c r="A41" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="B41" s="10">
-        <v>10</v>
+      <c r="B41" s="13" t="s">
+        <v>68</v>
       </c>
       <c r="C41" s="10">
         <v>0.25</v>
@@ -2478,8 +2671,8 @@
       <c r="A42" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B42" s="10">
-        <v>1</v>
+      <c r="B42" s="13" t="s">
+        <v>69</v>
       </c>
       <c r="C42" s="14">
         <v>0</v>
@@ -2507,8 +2700,8 @@
       <c r="A43" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B43" s="10">
-        <v>2</v>
+      <c r="B43" s="13" t="s">
+        <v>70</v>
       </c>
       <c r="C43" s="14">
         <v>0</v>
@@ -2536,8 +2729,8 @@
       <c r="A44" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B44" s="10">
-        <v>3</v>
+      <c r="B44" s="13" t="s">
+        <v>71</v>
       </c>
       <c r="C44" s="14">
         <v>0</v>
@@ -2565,8 +2758,8 @@
       <c r="A45" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B45" s="10">
-        <v>4</v>
+      <c r="B45" s="13" t="s">
+        <v>72</v>
       </c>
       <c r="C45" s="14">
         <v>0</v>
@@ -2594,8 +2787,8 @@
       <c r="A46" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B46" s="10">
-        <v>5</v>
+      <c r="B46" s="13" t="s">
+        <v>73</v>
       </c>
       <c r="C46" s="14">
         <v>0</v>
@@ -2623,8 +2816,8 @@
       <c r="A47" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B47" s="10">
-        <v>6</v>
+      <c r="B47" s="13" t="s">
+        <v>74</v>
       </c>
       <c r="C47" s="14">
         <v>0</v>
@@ -2652,8 +2845,8 @@
       <c r="A48" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B48" s="10">
-        <v>7</v>
+      <c r="B48" s="13" t="s">
+        <v>75</v>
       </c>
       <c r="C48" s="14">
         <v>0</v>
@@ -2681,8 +2874,8 @@
       <c r="A49" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B49" s="10">
-        <v>8</v>
+      <c r="B49" s="13" t="s">
+        <v>76</v>
       </c>
       <c r="C49" s="14">
         <v>0</v>
@@ -2710,8 +2903,8 @@
       <c r="A50" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B50" s="10">
-        <v>9</v>
+      <c r="B50" s="13" t="s">
+        <v>77</v>
       </c>
       <c r="C50" s="14">
         <v>0</v>
@@ -2739,8 +2932,8 @@
       <c r="A51" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="B51" s="10">
-        <v>10</v>
+      <c r="B51" s="13" t="s">
+        <v>78</v>
       </c>
       <c r="C51" s="14">
         <v>0</v>
@@ -2768,8 +2961,8 @@
       <c r="A52" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B52" s="10">
-        <v>1</v>
+      <c r="B52" s="13" t="s">
+        <v>79</v>
       </c>
       <c r="C52" s="10">
         <v>0.01</v>
@@ -2797,8 +2990,8 @@
       <c r="A53" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B53" s="10">
-        <v>2</v>
+      <c r="B53" s="13" t="s">
+        <v>80</v>
       </c>
       <c r="C53" s="10">
         <v>0.02</v>
@@ -2826,8 +3019,8 @@
       <c r="A54" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B54" s="10">
-        <v>3</v>
+      <c r="B54" s="13" t="s">
+        <v>81</v>
       </c>
       <c r="C54" s="10">
         <v>0.03</v>
@@ -2855,8 +3048,8 @@
       <c r="A55" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B55" s="10">
-        <v>4</v>
+      <c r="B55" s="13" t="s">
+        <v>82</v>
       </c>
       <c r="C55" s="10">
         <v>0.04</v>
@@ -2884,8 +3077,8 @@
       <c r="A56" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B56" s="10">
-        <v>5</v>
+      <c r="B56" s="13" t="s">
+        <v>83</v>
       </c>
       <c r="C56" s="10">
         <v>0.05</v>
@@ -2913,8 +3106,8 @@
       <c r="A57" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B57" s="10">
-        <v>6</v>
+      <c r="B57" s="13" t="s">
+        <v>84</v>
       </c>
       <c r="C57" s="10">
         <v>0.06</v>
@@ -2942,8 +3135,8 @@
       <c r="A58" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B58" s="10">
-        <v>7</v>
+      <c r="B58" s="13" t="s">
+        <v>85</v>
       </c>
       <c r="C58" s="10">
         <v>0.1</v>
@@ -2971,8 +3164,8 @@
       <c r="A59" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B59" s="10">
-        <v>8</v>
+      <c r="B59" s="13" t="s">
+        <v>86</v>
       </c>
       <c r="C59" s="10">
         <v>0.2</v>
@@ -3000,8 +3193,8 @@
       <c r="A60" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B60" s="10">
-        <v>9</v>
+      <c r="B60" s="13" t="s">
+        <v>87</v>
       </c>
       <c r="C60" s="10">
         <v>0.25</v>
@@ -3029,8 +3222,8 @@
       <c r="A61" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B61" s="10">
-        <v>10</v>
+      <c r="B61" s="13" t="s">
+        <v>88</v>
       </c>
       <c r="C61" s="10">
         <v>0.5</v>
